--- a/MainAPQP.xlsx
+++ b/MainAPQP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme\OneDrive\Desktop\gui\Programas\python\ExcelPython\Mehtal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guilherme\OneDrive\Desktop\gui\Programas\python\ExcelPython\Mehtal_v.1.0.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2F60989-DA53-4CE5-8C80-16A83B8FBFB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6470866B-56FD-41C4-8BE8-6F338D42BC73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="113">
   <si>
     <t>ABERTURA DE COTAÇÃO 2026</t>
   </si>
@@ -174,15 +174,9 @@
     <t>planta 7</t>
   </si>
   <si>
-    <t>Tipo 1</t>
-  </si>
-  <si>
     <t>Tipo 2</t>
   </si>
   <si>
-    <t>Tipo 3</t>
-  </si>
-  <si>
     <t>Tipo 4</t>
   </si>
   <si>
@@ -379,6 +373,9 @@
   </si>
   <si>
     <t>Shen</t>
+  </si>
+  <si>
+    <t>Protótipo</t>
   </si>
 </sst>
 </file>
@@ -388,7 +385,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -459,6 +456,12 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -583,7 +586,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -711,6 +714,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="10">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1223,7 +1227,7 @@
         <v>20</v>
       </c>
       <c r="T3" s="22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="U3" s="23" t="s">
         <v>21</v>
@@ -1240,7 +1244,7 @@
     </row>
     <row r="4" spans="2:24" s="1" customFormat="1" ht="12.75">
       <c r="B4" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C4" s="28" t="s">
         <v>25</v>
@@ -1253,28 +1257,28 @@
         <v>38</v>
       </c>
       <c r="G4" s="28" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="H4" s="28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="J4" s="30" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K4" s="30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L4" s="30" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="M4" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N4" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O4" s="31">
         <v>1111</v>
@@ -1287,13 +1291,13 @@
         <v>24472.25</v>
       </c>
       <c r="R4" s="26" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="S4" s="32" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="T4" s="26" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="U4" s="29">
         <v>46258</v>
@@ -1305,12 +1309,12 @@
         <v>46270</v>
       </c>
       <c r="X4" s="28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="2:24" s="1" customFormat="1" ht="13.5" customHeight="1">
       <c r="B5" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>26</v>
@@ -1323,28 +1327,28 @@
         <v>39</v>
       </c>
       <c r="G5" s="28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H5" s="28" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J5" s="30" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K5" s="30" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L5" s="30" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M5" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N5" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O5" s="31">
         <v>1111</v>
@@ -1357,13 +1361,13 @@
         <v>24472.25</v>
       </c>
       <c r="R5" s="26" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="S5" s="32" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="T5" s="26" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="U5" s="29">
         <v>46258</v>
@@ -1375,12 +1379,12 @@
         <v>46270</v>
       </c>
       <c r="X5" s="28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="2:24" s="1" customFormat="1" ht="13.5" customHeight="1">
       <c r="B6" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C6" s="28" t="s">
         <v>27</v>
@@ -1393,28 +1397,28 @@
         <v>40</v>
       </c>
       <c r="G6" s="28" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
       <c r="H6" s="28" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I6" s="30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K6" s="30" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="L6" s="30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M6" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="N6" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O6" s="31">
         <v>1111</v>
@@ -1427,13 +1431,13 @@
         <v>27188700</v>
       </c>
       <c r="R6" s="26" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="S6" s="32" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="T6" s="26" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="U6" s="29">
         <v>46258</v>
@@ -1445,12 +1449,12 @@
         <v>46270</v>
       </c>
       <c r="X6" s="28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="2:24" s="1" customFormat="1" ht="13.5" customHeight="1">
       <c r="B7" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>28</v>
@@ -1463,28 +1467,28 @@
         <v>41</v>
       </c>
       <c r="G7" s="28" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H7" s="28" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I7" s="30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K7" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L7" s="30" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M7" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N7" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O7" s="31">
         <v>1111</v>
@@ -1497,13 +1501,13 @@
         <v>27188700</v>
       </c>
       <c r="R7" s="26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S7" s="32" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="T7" s="26" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="U7" s="29">
         <v>46258</v>
@@ -1515,12 +1519,12 @@
         <v>46270</v>
       </c>
       <c r="X7" s="28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="2:24" s="1" customFormat="1" ht="13.5" customHeight="1">
       <c r="B8" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="28" t="s">
         <v>29</v>
@@ -1533,28 +1537,28 @@
         <v>42</v>
       </c>
       <c r="G8" s="28" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H8" s="28" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N8" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O8" s="31">
         <v>1111</v>
@@ -1567,13 +1571,13 @@
         <v>30206645730.25</v>
       </c>
       <c r="R8" s="26" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="S8" s="32" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="T8" s="26" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="U8" s="29">
         <v>46258</v>
@@ -1585,12 +1589,12 @@
         <v>46270</v>
       </c>
       <c r="X8" s="28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="2:24" s="1" customFormat="1" ht="13.5" customHeight="1">
       <c r="B9" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C9" s="28" t="s">
         <v>30</v>
@@ -1603,28 +1607,28 @@
         <v>43</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H9" s="28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L9" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M9" s="30" t="s">
-        <v>80</v>
-      </c>
       <c r="N9" s="30" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="O9" s="31">
         <v>1111</v>
@@ -1637,13 +1641,13 @@
         <v>30206645730.25</v>
       </c>
       <c r="R9" s="26" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="S9" s="32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="T9" s="26" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="U9" s="29">
         <v>46258</v>
@@ -1655,15 +1659,15 @@
         <v>46270</v>
       </c>
       <c r="X9" s="28" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="2:24" s="1" customFormat="1" ht="13.5" customHeight="1">
       <c r="B10" s="28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D10" s="28"/>
       <c r="E10" s="28" t="s">
@@ -1673,28 +1677,28 @@
         <v>44</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="I10" s="30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J10" s="30" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K10" s="30" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L10" s="30" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M10" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N10" s="30" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="O10" s="31">
         <v>1111</v>
@@ -1707,13 +1711,13 @@
         <v>33559583406338</v>
       </c>
       <c r="R10" s="26" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="S10" s="32" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="T10" s="26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U10" s="29">
         <v>46258</v>
@@ -1725,8 +1729,11 @@
         <v>46270</v>
       </c>
       <c r="X10" s="28" t="s">
-        <v>113</v>
-      </c>
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24">
+      <c r="L12" s="34"/>
     </row>
     <row r="13" spans="2:24" ht="15">
       <c r="C13" s="33"/>
